--- a/data/trans_dic/P8_1_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P8_1_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con limitación a hacer esfuerzos moderados</t>
+          <t>Población con limitación a hacer esfuerzos moderados (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,16; 26,15</t>
+          <t>20,98; 26,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28,52; 34,95</t>
+          <t>28,8; 35,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29,57; 35,88</t>
+          <t>29,72; 36,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29,52; 37,54</t>
+          <t>29,7; 37,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>38,92; 44,32</t>
+          <t>38,85; 44,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,75; 51,16</t>
+          <t>45,86; 51,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,34; 50,75</t>
+          <t>44,18; 51,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>50,59; 56,21</t>
+          <t>50,28; 56,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>31,81; 35,73</t>
+          <t>31,72; 35,65</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39,22; 43,39</t>
+          <t>39,59; 43,89</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38,72; 43,45</t>
+          <t>38,7; 43,63</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>42,79; 47,35</t>
+          <t>42,98; 47,74</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,59; 6,86</t>
+          <t>4,54; 6,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,83; 9,59</t>
+          <t>6,71; 9,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,74; 10,13</t>
+          <t>7,72; 10,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,19; 45,91</t>
+          <t>12,13; 47,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,24; 9,99</t>
+          <t>7,12; 9,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,28; 13,76</t>
+          <t>10,38; 13,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,51; 15,8</t>
+          <t>12,53; 15,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,75; 15,09</t>
+          <t>9,54; 15,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,17; 7,91</t>
+          <t>6,09; 7,82</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,85; 11,01</t>
+          <t>8,86; 11,01</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,44; 12,51</t>
+          <t>10,52; 12,5</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,48; 31,11</t>
+          <t>12,47; 33,51</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,4; 7,15</t>
+          <t>3,16; 7,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,89; 10,4</t>
+          <t>4,76; 10,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,79; 9,42</t>
+          <t>5,05; 9,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,7; 8,14</t>
+          <t>4,85; 8,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,42; 12,13</t>
+          <t>6,8; 12,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,19; 11,85</t>
+          <t>6,27; 11,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,1; 11,25</t>
+          <t>6,1; 11,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,05; 10,42</t>
+          <t>6,91; 10,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,32; 8,58</t>
+          <t>5,24; 8,69</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,2; 10,11</t>
+          <t>6,29; 10,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,07; 9,62</t>
+          <t>6,02; 9,4</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,28; 8,68</t>
+          <t>6,31; 8,62</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,18; 12,22</t>
+          <t>10,08; 12,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,38; 15,9</t>
+          <t>13,52; 15,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,6; 15,14</t>
+          <t>12,79; 15,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,36; 38,29</t>
+          <t>14,25; 37,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,0; 22,96</t>
+          <t>20,06; 22,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,69; 26,75</t>
+          <t>23,74; 26,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,19; 24,08</t>
+          <t>21,15; 24,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,22; 22,47</t>
+          <t>16,94; 22,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,49; 17,36</t>
+          <t>15,49; 17,21</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,17; 21,06</t>
+          <t>19,06; 20,98</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,42; 19,38</t>
+          <t>17,41; 19,31</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,38; 30,59</t>
+          <t>17,28; 30,38</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con limitación a hacer esfuerzos moderados</t>
+          <t>Población con limitación a hacer esfuerzos moderados (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>218306; 269842</t>
+          <t>216432; 271471</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>278004; 340654</t>
+          <t>280692; 342040</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>223061; 270665</t>
+          <t>224163; 278046</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>152017; 193315</t>
+          <t>152957; 193263</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>511903; 582904</t>
+          <t>510874; 580893</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>612054; 684425</t>
+          <t>613541; 687683</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>441051; 504785</t>
+          <t>439434; 507967</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>382184; 424687</t>
+          <t>379836; 426146</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>746635; 838503</t>
+          <t>744351; 836546</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>907011; 1003370</t>
+          <t>915602; 1014942</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>677154; 759872</t>
+          <t>676906; 763076</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>543588; 601495</t>
+          <t>546034; 606543</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>77804; 116252</t>
+          <t>76830; 115502</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>134175; 188340</t>
+          <t>131799; 182200</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>160649; 210257</t>
+          <t>160283; 212310</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>279127; 1051386</t>
+          <t>277828; 1084650</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>115007; 158576</t>
+          <t>113098; 155585</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>180633; 241799</t>
+          <t>182538; 238235</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>248760; 314108</t>
+          <t>249144; 312407</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>218216; 337797</t>
+          <t>213465; 338133</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>202480; 259608</t>
+          <t>199899; 256701</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>329221; 409938</t>
+          <t>329725; 409684</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>424156; 508427</t>
+          <t>427654; 508085</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>565004; 1408828</t>
+          <t>564816; 1517388</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18740; 39452</t>
+          <t>17427; 39248</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>23528; 50047</t>
+          <t>22889; 49262</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26212; 51496</t>
+          <t>27600; 54189</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30362; 52611</t>
+          <t>31368; 53957</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>30579; 57773</t>
+          <t>32382; 58337</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28400; 54366</t>
+          <t>28740; 54592</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33483; 61785</t>
+          <t>33501; 61140</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>46554; 68791</t>
+          <t>45610; 67685</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>54649; 88145</t>
+          <t>53900; 89295</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>58289; 95014</t>
+          <t>59090; 95757</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>66513; 105404</t>
+          <t>65997; 103035</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>82032; 113452</t>
+          <t>82424; 112628</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>333464; 400371</t>
+          <t>330433; 400334</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>457737; 543892</t>
+          <t>462357; 543531</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>425417; 511486</t>
+          <t>432045; 512273</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>495614; 1321774</t>
+          <t>491827; 1294866</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>675730; 775730</t>
+          <t>677917; 773902</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>841931; 950740</t>
+          <t>843770; 952259</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>748397; 850467</t>
+          <t>747127; 853288</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>592598; 821064</t>
+          <t>618877; 820308</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1030860; 1155726</t>
+          <t>1030826; 1145216</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1337111; 1468869</t>
+          <t>1329085; 1462864</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1203671; 1339066</t>
+          <t>1203077; 1334113</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1235107; 2173454</t>
+          <t>1227743; 2158417</t>
         </is>
       </c>
     </row>
